--- a/JsonConverter/ExcelFiles/EnemyBasic.xlsx
+++ b/JsonConverter/ExcelFiles/EnemyBasic.xlsx
@@ -5,11 +5,11 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\0_UnityProjects\Hero_Nursing\JsonConverter\ExcelFiles\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\NRUnityProjects\ACE\JsonConverter\ExcelFiles\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="22780" windowHeight="8480"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="28545" windowHeight="11745"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="EnemyBasic" sheetId="1" r:id="rId4"/>
@@ -19,90 +19,99 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="28">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+  <x:si>
+    <x:t>ProfileImage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로필이미지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 영문 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EnemyNameEn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy03</x:t>
+  </x:si>
   <x:si>
     <x:t>EnemyName</x:t>
   </x:si>
   <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemyNameEn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>enemy_01</x:t>
   </x:si>
   <x:si>
-    <x:t>enemy_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 영문 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적07</x:t>
+    <x:t>Image/Portrait_Enemy[enemy_01]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -902,72 +911,84 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:O35"/>
+  <x:dimension ref="A1:P35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="19.42578125" style="3" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="3" customWidth="1"/>
     <x:col min="3" max="3" width="24.7109375" style="3" customWidth="1"/>
-    <x:col min="4" max="4" width="20.28515625" style="3" customWidth="1"/>
-    <x:col min="5" max="5" width="30.5703125" style="3" customWidth="1"/>
-    <x:col min="6" max="6" width="26.5703125" style="3" customWidth="1"/>
-    <x:col min="7" max="16384" width="12.5703125" style="3"/>
+    <x:col min="4" max="4" width="29.85546875" style="3" customWidth="1"/>
+    <x:col min="5" max="5" width="20.28515625" style="3" customWidth="1"/>
+    <x:col min="6" max="6" width="30.5703125" style="3" customWidth="1"/>
+    <x:col min="7" max="7" width="26.5703125" style="3" customWidth="1"/>
+    <x:col min="8" max="16384" width="12.5703125" style="3"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D1" s="2"/>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D1" s="3" t="s">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="E1" s="2"/>
-    </x:row>
-    <x:row r="2" spans="1:6" ht="13.199999999999999">
+      <x:c r="F1" s="2"/>
+    </x:row>
+    <x:row r="2" spans="1:7" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="1"/>
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="D2" s="3" t="s">
+        <x:v>7</x:v>
+      </x:c>
       <x:c r="E2" s="1"/>
       <x:c r="F2" s="1"/>
-    </x:row>
-    <x:row r="3" spans="1:6" s="12" customFormat="1" ht="15.75" customHeight="1">
+      <x:c r="G2" s="1"/>
+    </x:row>
+    <x:row r="3" spans="1:7" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C3" s="11" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="D3" s="12" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="C3" s="11" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="13"/>
       <x:c r="E3" s="13"/>
-      <x:c r="F3" s="14"/>
-    </x:row>
-    <x:row r="4" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="F3" s="13"/>
+      <x:c r="G3" s="14"/>
+    </x:row>
+    <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="E4" s="5"/>
-      <x:c r="F4" s="15"/>
-      <x:c r="G4" s="5"/>
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="D4" s="5" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="F4" s="5"/>
+      <x:c r="G4" s="15"/>
       <x:c r="H4" s="5"/>
       <x:c r="I4" s="5"/>
       <x:c r="J4" s="5"/>
@@ -976,18 +997,19 @@
       <x:c r="M4" s="5"/>
       <x:c r="N4" s="5"/>
       <x:c r="O4" s="5"/>
-    </x:row>
-    <x:row r="5" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P4" s="5"/>
+    </x:row>
+    <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B5" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C5" s="4" t="s">
         <x:v>18</x:v>
       </x:c>
-      <x:c r="B5" s="4" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C5" s="4" t="s">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="E5" s="5"/>
+      <x:c r="D5" s="5"/>
       <x:c r="F5" s="5"/>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5"/>
@@ -998,18 +1020,19 @@
       <x:c r="M5" s="5"/>
       <x:c r="N5" s="5"/>
       <x:c r="O5" s="5"/>
-    </x:row>
-    <x:row r="6" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P5" s="5"/>
+    </x:row>
+    <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="E6" s="5"/>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D6" s="5"/>
       <x:c r="F6" s="5"/>
       <x:c r="G6" s="5"/>
       <x:c r="H6" s="5"/>
@@ -1020,18 +1043,19 @@
       <x:c r="M6" s="5"/>
       <x:c r="N6" s="5"/>
       <x:c r="O6" s="5"/>
-    </x:row>
-    <x:row r="7" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P6" s="5"/>
+    </x:row>
+    <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="E7" s="5"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D7" s="5"/>
       <x:c r="F7" s="5"/>
       <x:c r="G7" s="5"/>
       <x:c r="H7" s="5"/>
@@ -1042,18 +1066,19 @@
       <x:c r="M7" s="5"/>
       <x:c r="N7" s="5"/>
       <x:c r="O7" s="5"/>
-    </x:row>
-    <x:row r="8" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P7" s="5"/>
+    </x:row>
+    <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="E8" s="5"/>
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="D8" s="5"/>
       <x:c r="F8" s="5"/>
       <x:c r="G8" s="5"/>
       <x:c r="H8" s="5"/>
@@ -1064,18 +1089,19 @@
       <x:c r="M8" s="5"/>
       <x:c r="N8" s="5"/>
       <x:c r="O8" s="5"/>
-    </x:row>
-    <x:row r="9" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P8" s="5"/>
+    </x:row>
+    <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="E9" s="5"/>
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D9" s="5"/>
       <x:c r="F9" s="5"/>
       <x:c r="G9" s="5"/>
       <x:c r="H9" s="5"/>
@@ -1086,18 +1112,19 @@
       <x:c r="M9" s="5"/>
       <x:c r="N9" s="5"/>
       <x:c r="O9" s="5"/>
-    </x:row>
-    <x:row r="10" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P9" s="5"/>
+    </x:row>
+    <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="E10" s="5"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D10" s="5"/>
       <x:c r="F10" s="5"/>
       <x:c r="G10" s="5"/>
       <x:c r="H10" s="5"/>
@@ -1108,8 +1135,9 @@
       <x:c r="M10" s="5"/>
       <x:c r="N10" s="5"/>
       <x:c r="O10" s="5"/>
-    </x:row>
-    <x:row r="11" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P10" s="5"/>
+    </x:row>
+    <x:row r="11" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A11" s="1"/>
       <x:c r="B11" s="1"/>
       <x:c r="C11" s="1"/>
@@ -1125,8 +1153,9 @@
       <x:c r="M11" s="5"/>
       <x:c r="N11" s="5"/>
       <x:c r="O11" s="5"/>
-    </x:row>
-    <x:row r="12" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P11" s="5"/>
+    </x:row>
+    <x:row r="12" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A12" s="6"/>
       <x:c r="B12" s="6"/>
       <x:c r="C12" s="6"/>
@@ -1142,8 +1171,9 @@
       <x:c r="M12" s="5"/>
       <x:c r="N12" s="5"/>
       <x:c r="O12" s="5"/>
-    </x:row>
-    <x:row r="13" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P12" s="5"/>
+    </x:row>
+    <x:row r="13" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A13" s="4"/>
       <x:c r="B13" s="4"/>
       <x:c r="C13" s="4"/>
@@ -1159,8 +1189,9 @@
       <x:c r="M13" s="5"/>
       <x:c r="N13" s="5"/>
       <x:c r="O13" s="5"/>
-    </x:row>
-    <x:row r="14" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P13" s="5"/>
+    </x:row>
+    <x:row r="14" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A14" s="1"/>
       <x:c r="B14" s="1"/>
       <x:c r="C14" s="1"/>
@@ -1176,8 +1207,9 @@
       <x:c r="M14" s="5"/>
       <x:c r="N14" s="5"/>
       <x:c r="O14" s="5"/>
-    </x:row>
-    <x:row r="15" spans="1:15" ht="15.75" customHeight="1">
+      <x:c r="P14" s="5"/>
+    </x:row>
+    <x:row r="15" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A15" s="1"/>
       <x:c r="B15" s="1"/>
       <x:c r="C15" s="1"/>
@@ -1193,6 +1225,7 @@
       <x:c r="M15" s="5"/>
       <x:c r="N15" s="5"/>
       <x:c r="O15" s="5"/>
+      <x:c r="P15" s="5"/>
     </x:row>
     <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A16" s="7"/>
@@ -1209,12 +1242,12 @@
       <x:c r="B18" s="8"/>
       <x:c r="C18" s="8"/>
     </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="8"/>
       <x:c r="B19" s="8"/>
       <x:c r="C19" s="8"/>
-      <x:c r="D19" s="5"/>
       <x:c r="E19" s="5"/>
+      <x:c r="F19" s="5"/>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A20" s="8"/>
@@ -1241,29 +1274,29 @@
       <x:c r="B24" s="8"/>
       <x:c r="C24" s="8"/>
     </x:row>
-    <x:row r="25" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="25" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A25" s="8"/>
       <x:c r="B25" s="8"/>
       <x:c r="C25" s="8"/>
-      <x:c r="E25" s="5"/>
-    </x:row>
-    <x:row r="26" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F25" s="5"/>
+    </x:row>
+    <x:row r="26" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A26" s="9"/>
       <x:c r="B26" s="9"/>
       <x:c r="C26" s="9"/>
-      <x:c r="E26" s="5"/>
-    </x:row>
-    <x:row r="27" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F26" s="5"/>
+    </x:row>
+    <x:row r="27" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A27" s="9"/>
       <x:c r="B27" s="9"/>
       <x:c r="C27" s="9"/>
-      <x:c r="E27" s="5"/>
-    </x:row>
-    <x:row r="28" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="F27" s="5"/>
+    </x:row>
+    <x:row r="28" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A28" s="9"/>
       <x:c r="B28" s="9"/>
       <x:c r="C28" s="9"/>
-      <x:c r="E28" s="5"/>
+      <x:c r="F28" s="5"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A29" s="9"/>
@@ -2266,7 +2299,7 @@
     <x:row r="999" ht="15.75" customHeight="1"/>
     <x:row r="1000" ht="15.75" customHeight="1"/>
   </x:sheetData>
-  <x:pageMargins left="0.69986110925674438" right="0.69986110925674438" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
+  <x:pageMargins left="0.69972223043441772" right="0.69972223043441772" top="0.75" bottom="0.75" header="0.30000001192092896" footer="0.30000001192092896"/>
   <x:pageSetup paperSize="9" scale="100" firstPageNumber="1" fitToWidth="1" fitToHeight="1" orientation="portrait" usePrinterDefaults="1" blackAndWhite="0" draft="0" useFirstPageNumber="0" horizontalDpi="600" verticalDpi="600" copies="1"/>
 </x:worksheet>
 </file>
--- a/JsonConverter/ExcelFiles/EnemyBasic.xlsx
+++ b/JsonConverter/ExcelFiles/EnemyBasic.xlsx
@@ -21,97 +21,97 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
   <x:si>
+    <x:t>센티널</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Blackguard Soldier</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Portrait_Enemy[enemy_01]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EnemyName</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EnemyNameEn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sentinel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블랙가드 병사</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로필이미지</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 영문 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적03</x:t>
+  </x:si>
+  <x:si>
     <x:t>ProfileImage</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로필이미지</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 영문 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemyNameEn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemyName</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_01</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Image/Portrait_Enemy[enemy_01]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -929,29 +929,29 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>6</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
     </x:row>
     <x:row r="2" spans="1:7" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>7</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E2" s="1"/>
       <x:c r="F2" s="1"/>
@@ -962,13 +962,13 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>28</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
-        <x:v>0</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E3" s="13"/>
       <x:c r="F3" s="13"/>
@@ -976,16 +976,16 @@
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>29</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>30</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F4" s="5"/>
       <x:c r="G4" s="15"/>
@@ -1001,10 +1001,10 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
         <x:v>18</x:v>
@@ -1024,13 +1024,13 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D6" s="5"/>
       <x:c r="F6" s="5"/>
@@ -1047,13 +1047,13 @@
     </x:row>
     <x:row r="7" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A7" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D7" s="5"/>
       <x:c r="F7" s="5"/>
@@ -1070,13 +1070,13 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>23</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C8" s="4" t="s">
         <x:v>13</x:v>
-      </x:c>
-      <x:c r="C8" s="4" t="s">
-        <x:v>21</x:v>
       </x:c>
       <x:c r="D8" s="5"/>
       <x:c r="F8" s="5"/>
@@ -1093,13 +1093,13 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D9" s="5"/>
       <x:c r="F9" s="5"/>
@@ -1116,13 +1116,13 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>26</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D10" s="5"/>
       <x:c r="F10" s="5"/>

--- a/JsonConverter/ExcelFiles/EnemyBasic.xlsx
+++ b/JsonConverter/ExcelFiles/EnemyBasic.xlsx
@@ -19,78 +19,87 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="32">
+  <x:si>
+    <x:t>Image/Portrait_Enemy[enemy_01]</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ID</x:t>
+  </x:si>
   <x:si>
     <x:t>센티널</x:t>
   </x:si>
   <x:si>
-    <x:t>ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>적ID</x:t>
   </x:si>
   <x:si>
     <x:t>Blackguard Soldier</x:t>
   </x:si>
   <x:si>
-    <x:t>Image/Portrait_Enemy[enemy_01]</x:t>
+    <x:t>TempEnemy06</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sentinel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EnemyNameEn</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>enemy_03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TempEnemy03</x:t>
   </x:si>
   <x:si>
     <x:t>enemy_07</x:t>
   </x:si>
   <x:si>
-    <x:t>TempEnemy03</x:t>
-  </x:si>
-  <x:si>
     <x:t>EnemyName</x:t>
   </x:si>
   <x:si>
     <x:t>enemy_06</x:t>
   </x:si>
   <x:si>
-    <x:t>enemy_05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TempEnemy07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EnemyNameEn</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Sentinel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>enemy_01</x:t>
-  </x:si>
-  <x:si>
     <x:t>블랙가드 병사</x:t>
   </x:si>
   <x:si>
+    <x:t>임시적05</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>임시적06</x:t>
+  </x:si>
+  <x:si>
     <x:t>임시적04</x:t>
   </x:si>
   <x:si>
-    <x:t>임시적05</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>적 영문 이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>적 이름</x:t>
   </x:si>
   <x:si>
     <x:t>프로필이미지</x:t>
@@ -99,19 +108,13 @@
     <x:t>임시적07</x:t>
   </x:si>
   <x:si>
-    <x:t>적 영문 이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t>임시적06</x:t>
-  </x:si>
-  <x:si>
-    <x:t>적 이름</x:t>
-  </x:si>
-  <x:si>
     <x:t>임시적03</x:t>
   </x:si>
   <x:si>
     <x:t>ProfileImage</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Image/Portrait_Enemy[enemy_02]</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -926,32 +929,32 @@
   <x:sheetData>
     <x:row r="1" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B1" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D1" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E1" s="2"/>
       <x:c r="F1" s="2"/>
     </x:row>
     <x:row r="2" spans="1:7" ht="13.199999999999999">
       <x:c r="A2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D2" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E2" s="1"/>
       <x:c r="F2" s="1"/>
@@ -962,10 +965,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="12" t="s">
         <x:v>30</x:v>
@@ -976,16 +979,16 @@
     </x:row>
     <x:row r="4" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A4" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B4" s="4" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F4" s="5"/>
       <x:c r="G4" s="15"/>
@@ -1001,15 +1004,17 @@
     </x:row>
     <x:row r="5" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A5" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="D5" s="5"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D5" s="5" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="F5" s="5"/>
       <x:c r="G5" s="5"/>
       <x:c r="H5" s="5"/>
@@ -1024,13 +1029,13 @@
     </x:row>
     <x:row r="6" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A6" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
         <x:v>29</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D6" s="5"/>
       <x:c r="F6" s="5"/>
@@ -1050,10 +1055,10 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D7" s="5"/>
       <x:c r="F7" s="5"/>
@@ -1070,13 +1075,13 @@
     </x:row>
     <x:row r="8" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A8" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B8" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C8" s="4" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D8" s="5"/>
       <x:c r="F8" s="5"/>
@@ -1093,13 +1098,13 @@
     </x:row>
     <x:row r="9" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A9" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B9" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C9" s="4" t="s">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D9" s="5"/>
       <x:c r="F9" s="5"/>
@@ -1116,13 +1121,13 @@
     </x:row>
     <x:row r="10" spans="1:16" ht="15.75" customHeight="1">
       <x:c r="A10" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B10" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C10" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D10" s="5"/>
       <x:c r="F10" s="5"/>
